--- a/qwq-score/TFGAN/qw3-0705/aT0-By0516_t0_T0.6thinking_f/abf10_sum.xlsx
+++ b/qwq-score/TFGAN/qw3-0705/aT0-By0516_t0_T0.6thinking_f/abf10_sum.xlsx
@@ -461,12 +461,18 @@
           <t>0718_01.txt</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>60</v>
+      </c>
+      <c r="D2" t="n">
+        <v>45</v>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>找到Final Scores但无法解析内容</t>
+          <t>发现2个有效块 - 使用最后一个</t>
         </is>
       </c>
     </row>
@@ -476,12 +482,18 @@
           <t>0722_01.txt</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
+      <c r="B3" t="n">
+        <v>90</v>
+      </c>
+      <c r="C3" t="n">
+        <v>85</v>
+      </c>
+      <c r="D3" t="n">
+        <v>70</v>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>找到Final Scores但无法解析内容</t>
+          <t>发现2个有效块 - 使用最后一个</t>
         </is>
       </c>
     </row>
@@ -491,12 +503,18 @@
           <t>0722_02.txt</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
+      <c r="B4" t="n">
+        <v>32</v>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>10</v>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>找到Final Scores但无法解析内容</t>
+          <t>发现2个有效块 - 使用最后一个</t>
         </is>
       </c>
     </row>
@@ -506,12 +524,18 @@
           <t>0722_03.txt</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+      <c r="B5" t="n">
+        <v>85</v>
+      </c>
+      <c r="C5" t="n">
+        <v>85</v>
+      </c>
+      <c r="D5" t="n">
+        <v>100</v>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>找到Final Scores但无法解析内容</t>
+          <t>成功提取</t>
         </is>
       </c>
     </row>
@@ -521,12 +545,18 @@
           <t>0722_04.txt</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+      <c r="B6" t="n">
+        <v>80</v>
+      </c>
+      <c r="C6" t="n">
+        <v>70</v>
+      </c>
+      <c r="D6" t="n">
+        <v>83</v>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>找到Final Scores但无法解析内容</t>
+          <t>成功提取</t>
         </is>
       </c>
     </row>
@@ -536,12 +566,18 @@
           <t>0722_05.txt</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
+      <c r="B7" t="n">
+        <v>90</v>
+      </c>
+      <c r="C7" t="n">
+        <v>65</v>
+      </c>
+      <c r="D7" t="n">
+        <v>100</v>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>找到Final Scores但无法解析内容</t>
+          <t>发现3个有效块 - 使用最后一个</t>
         </is>
       </c>
     </row>
@@ -551,12 +587,18 @@
           <t>0722_06.txt</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
+      <c r="B8" t="n">
+        <v>74.17</v>
+      </c>
+      <c r="C8" t="n">
+        <v>55</v>
+      </c>
+      <c r="D8" t="n">
+        <v>60</v>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>找到Final Scores但无法解析内容</t>
+          <t>成功提取</t>
         </is>
       </c>
     </row>
@@ -566,12 +608,18 @@
           <t>0722_07.txt</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+      <c r="B9" t="n">
+        <v>79</v>
+      </c>
+      <c r="C9" t="n">
+        <v>61</v>
+      </c>
+      <c r="D9" t="n">
+        <v>80</v>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>找到Final Scores但无法解析内容</t>
+          <t>成功提取</t>
         </is>
       </c>
     </row>
@@ -581,12 +629,18 @@
           <t>0722_08.txt</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
+      <c r="B10" t="n">
+        <v>80</v>
+      </c>
+      <c r="C10" t="n">
+        <v>49</v>
+      </c>
+      <c r="D10" t="n">
+        <v>10</v>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>找到Final Scores但无法解析内容</t>
+          <t>成功提取</t>
         </is>
       </c>
     </row>
@@ -596,12 +650,18 @@
           <t>0722_09.txt</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
+      <c r="B11" t="n">
+        <v>56</v>
+      </c>
+      <c r="C11" t="n">
+        <v>35</v>
+      </c>
+      <c r="D11" t="n">
+        <v>10</v>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>找到Final Scores但无法解析内容</t>
+          <t>发现2个有效块 - 使用最后一个</t>
         </is>
       </c>
     </row>
@@ -611,12 +671,18 @@
           <t>0722_10.txt</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
+      <c r="B12" t="n">
+        <v>90</v>
+      </c>
+      <c r="C12" t="n">
+        <v>75</v>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>找到Final Scores但无法解析内容</t>
+          <t>发现2个有效块 - 使用最后一个</t>
         </is>
       </c>
     </row>
@@ -626,12 +692,18 @@
           <t>0722_11.txt</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>45</v>
+      </c>
+      <c r="D13" t="n">
+        <v>65</v>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>找到Final Scores但无法解析内容</t>
+          <t>成功提取</t>
         </is>
       </c>
     </row>
@@ -641,12 +713,18 @@
           <t>0722_12.txt</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
+      <c r="B14" t="n">
+        <v>65</v>
+      </c>
+      <c r="C14" t="n">
+        <v>50</v>
+      </c>
+      <c r="D14" t="n">
+        <v>60</v>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>找到Final Scores但无法解析内容</t>
+          <t>发现2个有效块 - 使用最后一个</t>
         </is>
       </c>
     </row>
@@ -656,12 +734,18 @@
           <t>0722_13.txt</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+      <c r="B15" t="n">
+        <v>80</v>
+      </c>
+      <c r="C15" t="n">
+        <v>65</v>
+      </c>
+      <c r="D15" t="n">
+        <v>90</v>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>找到Final Scores但无法解析内容</t>
+          <t>发现2个有效块 - 使用最后一个</t>
         </is>
       </c>
     </row>
@@ -671,12 +755,18 @@
           <t>0722_14.txt</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
+      <c r="B16" t="n">
+        <v>77</v>
+      </c>
+      <c r="C16" t="n">
+        <v>79</v>
+      </c>
+      <c r="D16" t="n">
+        <v>78</v>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>找到Final Scores但无法解析内容</t>
+          <t>发现2个有效块 - 使用最后一个</t>
         </is>
       </c>
     </row>
@@ -686,12 +776,18 @@
           <t>0722_15.txt</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
+      <c r="B17" t="n">
+        <v>78</v>
+      </c>
+      <c r="C17" t="n">
+        <v>64</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>找到Final Scores但无法解析内容</t>
+          <t>成功提取</t>
         </is>
       </c>
     </row>
@@ -701,12 +797,18 @@
           <t>0722_16.txt</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+      <c r="B18" t="n">
+        <v>73</v>
+      </c>
+      <c r="C18" t="n">
+        <v>38</v>
+      </c>
+      <c r="D18" t="n">
+        <v>70</v>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>找到Final Scores但无法解析内容</t>
+          <t>成功提取</t>
         </is>
       </c>
     </row>
@@ -716,12 +818,18 @@
           <t>0722_17.txt</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
+      <c r="B19" t="n">
+        <v>78</v>
+      </c>
+      <c r="C19" t="n">
+        <v>79</v>
+      </c>
+      <c r="D19" t="n">
+        <v>63</v>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>找到Final Scores但无法解析内容</t>
+          <t>发现2个有效块 - 使用最后一个</t>
         </is>
       </c>
     </row>
@@ -731,12 +839,18 @@
           <t>0722_18.txt</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
+      <c r="B20" t="n">
+        <v>90</v>
+      </c>
+      <c r="C20" t="n">
+        <v>70</v>
+      </c>
+      <c r="D20" t="n">
+        <v>75</v>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>找到Final Scores但无法解析内容</t>
+          <t>成功提取</t>
         </is>
       </c>
     </row>
@@ -746,12 +860,18 @@
           <t>0722_19.txt</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
+      <c r="B21" t="n">
+        <v>100</v>
+      </c>
+      <c r="C21" t="n">
+        <v>75</v>
+      </c>
+      <c r="D21" t="n">
+        <v>87</v>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>找到Final Scores但无法解析内容</t>
+          <t>成功提取</t>
         </is>
       </c>
     </row>
@@ -761,12 +881,18 @@
           <t>0722_20.txt</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
+      <c r="B22" t="n">
+        <v>75</v>
+      </c>
+      <c r="C22" t="n">
+        <v>90</v>
+      </c>
+      <c r="D22" t="n">
+        <v>63</v>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>找到Final Scores但无法解析内容</t>
+          <t>发现2个有效块 - 使用最后一个</t>
         </is>
       </c>
     </row>
